--- a/tests/сводка.xlsx
+++ b/tests/сводка.xlsx
@@ -34,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -56,11 +56,27 @@
       <right style="hair"/>
       <top style="hair"/>
     </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -69,6 +85,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:O20"/>
+  <dimension ref="B2:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -517,6 +536,197 @@
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="5" t="n"/>
     </row>
+    <row r="7">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>0-4 с.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>5 с.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>6 с.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>7 с.</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>некондиция</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>общая</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>выхода</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n"/>
+      <c r="D9" s="1" t="n"/>
+      <c r="E9" s="1" t="n"/>
+      <c r="F9" s="1" t="n"/>
+      <c r="G9" s="1" t="n"/>
+      <c r="H9" s="1" t="n"/>
+      <c r="I9" s="1" t="n"/>
+      <c r="J9" s="1" t="n"/>
+      <c r="K9" s="1" t="n"/>
+      <c r="L9" s="1" t="n"/>
+      <c r="M9" s="1" t="n"/>
+      <c r="N9" s="1" t="n"/>
+      <c r="O9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>3 м</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+      <c r="H10" s="1" t="n"/>
+      <c r="I10" s="1" t="n"/>
+      <c r="J10" s="1" t="n"/>
+      <c r="K10" s="1" t="n"/>
+      <c r="L10" s="1" t="n"/>
+      <c r="M10" s="1" t="n"/>
+      <c r="N10" s="1" t="n"/>
+      <c r="O10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2 м</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
+      <c r="H11" s="1" t="n"/>
+      <c r="I11" s="1" t="n"/>
+      <c r="J11" s="1" t="n"/>
+      <c r="K11" s="1" t="n"/>
+      <c r="L11" s="1" t="n"/>
+      <c r="M11" s="1" t="n"/>
+      <c r="N11" s="1" t="n"/>
+      <c r="O11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Итого:</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="7" t="n"/>
+      <c r="O12" s="8" t="n"/>
+    </row>
     <row r="13">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="2" t="inlineStr">
@@ -536,6 +746,197 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="5" t="n"/>
     </row>
+    <row r="14">
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>0-4 с.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>5 с.</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>6 с.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>7 с.</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>некондиция</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>общая</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>выхода</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
+      <c r="G16" s="1" t="n"/>
+      <c r="H16" s="1" t="n"/>
+      <c r="I16" s="1" t="n"/>
+      <c r="J16" s="1" t="n"/>
+      <c r="K16" s="1" t="n"/>
+      <c r="L16" s="1" t="n"/>
+      <c r="M16" s="1" t="n"/>
+      <c r="N16" s="1" t="n"/>
+      <c r="O16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>3 м</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n"/>
+      <c r="D17" s="1" t="n"/>
+      <c r="E17" s="1" t="n"/>
+      <c r="F17" s="1" t="n"/>
+      <c r="G17" s="1" t="n"/>
+      <c r="H17" s="1" t="n"/>
+      <c r="I17" s="1" t="n"/>
+      <c r="J17" s="1" t="n"/>
+      <c r="K17" s="1" t="n"/>
+      <c r="L17" s="1" t="n"/>
+      <c r="M17" s="1" t="n"/>
+      <c r="N17" s="1" t="n"/>
+      <c r="O17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2 м</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="G18" s="1" t="n"/>
+      <c r="H18" s="1" t="n"/>
+      <c r="I18" s="1" t="n"/>
+      <c r="J18" s="1" t="n"/>
+      <c r="K18" s="1" t="n"/>
+      <c r="L18" s="1" t="n"/>
+      <c r="M18" s="1" t="n"/>
+      <c r="N18" s="1" t="n"/>
+      <c r="O18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Итого:</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
+      <c r="O19" s="8" t="n"/>
+    </row>
     <row r="20">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="2" t="inlineStr">
@@ -555,19 +956,225 @@
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="5" t="n"/>
     </row>
+    <row r="21">
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>0-4 с.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>5 с.</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>6 с.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>7 с.</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>некондиция</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t>общая</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="L22" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="M22" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="N22" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>выхода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n"/>
+      <c r="D23" s="1" t="n"/>
+      <c r="E23" s="1" t="n"/>
+      <c r="F23" s="1" t="n"/>
+      <c r="G23" s="1" t="n"/>
+      <c r="H23" s="1" t="n"/>
+      <c r="I23" s="1" t="n"/>
+      <c r="J23" s="1" t="n"/>
+      <c r="K23" s="1" t="n"/>
+      <c r="L23" s="1" t="n"/>
+      <c r="M23" s="1" t="n"/>
+      <c r="N23" s="1" t="n"/>
+      <c r="O23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>3 м</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n"/>
+      <c r="D24" s="1" t="n"/>
+      <c r="E24" s="1" t="n"/>
+      <c r="F24" s="1" t="n"/>
+      <c r="G24" s="1" t="n"/>
+      <c r="H24" s="1" t="n"/>
+      <c r="I24" s="1" t="n"/>
+      <c r="J24" s="1" t="n"/>
+      <c r="K24" s="1" t="n"/>
+      <c r="L24" s="1" t="n"/>
+      <c r="M24" s="1" t="n"/>
+      <c r="N24" s="1" t="n"/>
+      <c r="O24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2 м</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n"/>
+      <c r="D25" s="1" t="n"/>
+      <c r="E25" s="1" t="n"/>
+      <c r="F25" s="1" t="n"/>
+      <c r="G25" s="1" t="n"/>
+      <c r="H25" s="1" t="n"/>
+      <c r="I25" s="1" t="n"/>
+      <c r="J25" s="1" t="n"/>
+      <c r="K25" s="1" t="n"/>
+      <c r="L25" s="1" t="n"/>
+      <c r="M25" s="1" t="n"/>
+      <c r="N25" s="1" t="n"/>
+      <c r="O25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Итого:</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
+      <c r="N26" s="7" t="n"/>
+      <c r="O26" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="26">
+    <mergeCell ref="G21:H21"/>
     <mergeCell ref="K3:O3"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="K14:L14"/>
     <mergeCell ref="G2:O2"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="E5:J5"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="K5:O5"/>
     <mergeCell ref="E4:J4"/>
-    <mergeCell ref="E3:J3"/>
     <mergeCell ref="K4:O4"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/сводка.xlsx
+++ b/tests/сводка.xlsx
@@ -17,13 +17,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -99,15 +103,41 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -496,71 +526,87 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ДАТА</t>
+        </is>
+      </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>БРИГАДА</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="5" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1" t="n"/>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Распилено пиловочника</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="1" t="n"/>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>штук</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="7" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="3" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1" t="n"/>
+      <c r="A3" s="7" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="1" t="n"/>
+      <c r="D3" s="7" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
-      <c r="J3" s="1" t="n"/>
+      <c r="J3" s="7" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="3" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1" t="n"/>
+      <c r="A4" s="7" t="n"/>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="1" t="n"/>
+      <c r="D4" s="7" t="n"/>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
-      <c r="J4" s="1" t="n"/>
+      <c r="J4" s="7" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1" t="n"/>
+      <c r="A5" s="7" t="n"/>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
@@ -576,103 +622,103 @@
       <c r="N5" s="3" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="1" t="n"/>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" s="1" t="n"/>
+      <c r="F6" s="7" t="n"/>
       <c r="G6" s="2" t="n"/>
-      <c r="H6" s="1" t="n"/>
+      <c r="H6" s="7" t="n"/>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="1" t="n"/>
+      <c r="J6" s="7" t="n"/>
       <c r="K6" s="2" t="n"/>
-      <c r="L6" s="1" t="n"/>
-      <c r="M6" s="1" t="n"/>
-      <c r="N6" s="4" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="8" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="1" t="n"/>
-      <c r="C7" s="1" t="n"/>
-      <c r="D7" s="1" t="n"/>
-      <c r="E7" s="1" t="n"/>
-      <c r="F7" s="1" t="n"/>
-      <c r="G7" s="1" t="n"/>
-      <c r="H7" s="1" t="n"/>
-      <c r="I7" s="1" t="n"/>
-      <c r="J7" s="1" t="n"/>
-      <c r="K7" s="1" t="n"/>
-      <c r="L7" s="1" t="n"/>
-      <c r="M7" s="1" t="n"/>
-      <c r="N7" s="4" t="n"/>
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="8" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="1" t="n"/>
-      <c r="C8" s="1" t="n"/>
-      <c r="D8" s="1" t="n"/>
-      <c r="E8" s="1" t="n"/>
-      <c r="F8" s="1" t="n"/>
-      <c r="G8" s="1" t="n"/>
-      <c r="H8" s="1" t="n"/>
-      <c r="I8" s="1" t="n"/>
-      <c r="J8" s="1" t="n"/>
-      <c r="K8" s="1" t="n"/>
-      <c r="L8" s="1" t="n"/>
-      <c r="M8" s="1" t="n"/>
-      <c r="N8" s="4" t="n"/>
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="8" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="n"/>
-      <c r="C9" s="1" t="n"/>
-      <c r="D9" s="1" t="n"/>
-      <c r="E9" s="1" t="n"/>
-      <c r="F9" s="1" t="n"/>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="n"/>
-      <c r="I9" s="1" t="n"/>
-      <c r="J9" s="1" t="n"/>
-      <c r="K9" s="1" t="n"/>
-      <c r="L9" s="1" t="n"/>
-      <c r="M9" s="1" t="n"/>
-      <c r="N9" s="4" t="n"/>
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="8" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="1" t="n"/>
-      <c r="C10" s="1" t="n"/>
-      <c r="D10" s="1" t="n"/>
-      <c r="E10" s="1" t="n"/>
-      <c r="F10" s="1" t="n"/>
-      <c r="G10" s="1" t="n"/>
-      <c r="H10" s="1" t="n"/>
-      <c r="I10" s="1" t="n"/>
-      <c r="J10" s="1" t="n"/>
-      <c r="K10" s="1" t="n"/>
-      <c r="L10" s="1" t="n"/>
-      <c r="M10" s="1" t="n"/>
-      <c r="N10" s="4" t="n"/>
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="8" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="n"/>
-      <c r="C11" s="1" t="n"/>
-      <c r="D11" s="1" t="n"/>
-      <c r="E11" s="1" t="n"/>
-      <c r="F11" s="1" t="n"/>
-      <c r="G11" s="1" t="n"/>
-      <c r="H11" s="1" t="n"/>
-      <c r="I11" s="1" t="n"/>
-      <c r="J11" s="1" t="n"/>
-      <c r="K11" s="1" t="n"/>
-      <c r="L11" s="1" t="n"/>
-      <c r="M11" s="1" t="n"/>
-      <c r="N11" s="4" t="n"/>
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="8" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="7" t="n"/>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
@@ -688,103 +734,103 @@
       <c r="N12" s="3" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="1" t="n"/>
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="1" t="n"/>
+      <c r="D13" s="7" t="n"/>
       <c r="E13" s="2" t="n"/>
-      <c r="F13" s="1" t="n"/>
+      <c r="F13" s="7" t="n"/>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="1" t="n"/>
+      <c r="H13" s="7" t="n"/>
       <c r="I13" s="2" t="n"/>
-      <c r="J13" s="1" t="n"/>
+      <c r="J13" s="7" t="n"/>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="1" t="n"/>
-      <c r="M13" s="1" t="n"/>
-      <c r="N13" s="4" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="8" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="1" t="n"/>
-      <c r="E14" s="1" t="n"/>
-      <c r="F14" s="1" t="n"/>
-      <c r="G14" s="1" t="n"/>
-      <c r="H14" s="1" t="n"/>
-      <c r="I14" s="1" t="n"/>
-      <c r="J14" s="1" t="n"/>
-      <c r="K14" s="1" t="n"/>
-      <c r="L14" s="1" t="n"/>
-      <c r="M14" s="1" t="n"/>
-      <c r="N14" s="4" t="n"/>
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="8" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="1" t="n"/>
-      <c r="E15" s="1" t="n"/>
-      <c r="F15" s="1" t="n"/>
-      <c r="G15" s="1" t="n"/>
-      <c r="H15" s="1" t="n"/>
-      <c r="I15" s="1" t="n"/>
-      <c r="J15" s="1" t="n"/>
-      <c r="K15" s="1" t="n"/>
-      <c r="L15" s="1" t="n"/>
-      <c r="M15" s="1" t="n"/>
-      <c r="N15" s="4" t="n"/>
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="8" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
-      <c r="G16" s="1" t="n"/>
-      <c r="H16" s="1" t="n"/>
-      <c r="I16" s="1" t="n"/>
-      <c r="J16" s="1" t="n"/>
-      <c r="K16" s="1" t="n"/>
-      <c r="L16" s="1" t="n"/>
-      <c r="M16" s="1" t="n"/>
-      <c r="N16" s="4" t="n"/>
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="8" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="1" t="n"/>
-      <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="n"/>
-      <c r="E17" s="1" t="n"/>
-      <c r="F17" s="1" t="n"/>
-      <c r="G17" s="1" t="n"/>
-      <c r="H17" s="1" t="n"/>
-      <c r="I17" s="1" t="n"/>
-      <c r="J17" s="1" t="n"/>
-      <c r="K17" s="1" t="n"/>
-      <c r="L17" s="1" t="n"/>
-      <c r="M17" s="1" t="n"/>
-      <c r="N17" s="4" t="n"/>
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="8" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="G18" s="1" t="n"/>
-      <c r="H18" s="1" t="n"/>
-      <c r="I18" s="1" t="n"/>
-      <c r="J18" s="1" t="n"/>
-      <c r="K18" s="1" t="n"/>
-      <c r="L18" s="1" t="n"/>
-      <c r="M18" s="1" t="n"/>
-      <c r="N18" s="4" t="n"/>
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="8" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="1" t="n"/>
+      <c r="A19" s="7" t="n"/>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
@@ -800,102 +846,106 @@
       <c r="N19" s="3" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="1" t="n"/>
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="2" t="n"/>
-      <c r="D20" s="1" t="n"/>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="2" t="n"/>
-      <c r="F20" s="1" t="n"/>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" s="2" t="n"/>
-      <c r="H20" s="1" t="n"/>
+      <c r="H20" s="7" t="n"/>
       <c r="I20" s="2" t="n"/>
-      <c r="J20" s="1" t="n"/>
+      <c r="J20" s="7" t="n"/>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="1" t="n"/>
-      <c r="M20" s="1" t="n"/>
-      <c r="N20" s="4" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="8" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="1" t="n"/>
-      <c r="C21" s="1" t="n"/>
-      <c r="D21" s="1" t="n"/>
-      <c r="E21" s="1" t="n"/>
-      <c r="F21" s="1" t="n"/>
-      <c r="G21" s="1" t="n"/>
-      <c r="H21" s="1" t="n"/>
-      <c r="I21" s="1" t="n"/>
-      <c r="J21" s="1" t="n"/>
-      <c r="K21" s="1" t="n"/>
-      <c r="L21" s="1" t="n"/>
-      <c r="M21" s="1" t="n"/>
-      <c r="N21" s="4" t="n"/>
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="8" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="1" t="n"/>
-      <c r="B22" s="1" t="n"/>
-      <c r="C22" s="1" t="n"/>
-      <c r="D22" s="1" t="n"/>
-      <c r="E22" s="1" t="n"/>
-      <c r="F22" s="1" t="n"/>
-      <c r="G22" s="1" t="n"/>
-      <c r="H22" s="1" t="n"/>
-      <c r="I22" s="1" t="n"/>
-      <c r="J22" s="1" t="n"/>
-      <c r="K22" s="1" t="n"/>
-      <c r="L22" s="1" t="n"/>
-      <c r="M22" s="1" t="n"/>
-      <c r="N22" s="4" t="n"/>
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
+      <c r="N22" s="8" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="1" t="n"/>
-      <c r="C23" s="1" t="n"/>
-      <c r="D23" s="1" t="n"/>
-      <c r="E23" s="1" t="n"/>
-      <c r="F23" s="1" t="n"/>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="n"/>
-      <c r="K23" s="1" t="n"/>
-      <c r="L23" s="1" t="n"/>
-      <c r="M23" s="1" t="n"/>
-      <c r="N23" s="4" t="n"/>
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="8" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="1" t="n"/>
-      <c r="C24" s="1" t="n"/>
-      <c r="D24" s="1" t="n"/>
-      <c r="E24" s="1" t="n"/>
-      <c r="F24" s="1" t="n"/>
-      <c r="G24" s="1" t="n"/>
-      <c r="H24" s="1" t="n"/>
-      <c r="I24" s="1" t="n"/>
-      <c r="J24" s="1" t="n"/>
-      <c r="K24" s="1" t="n"/>
-      <c r="L24" s="1" t="n"/>
-      <c r="M24" s="1" t="n"/>
-      <c r="N24" s="4" t="n"/>
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="7" t="n"/>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
+      <c r="N24" s="8" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="6" t="n"/>
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="10" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="E1:N1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tests/сводка.xlsx
+++ b/tests/сводка.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -103,42 +103,26 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -538,16 +522,16 @@
           <t>БРИГАДА</t>
         </is>
       </c>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
-      <c r="K1" s="4" t="n"/>
-      <c r="L1" s="4" t="n"/>
-      <c r="M1" s="4" t="n"/>
-      <c r="N1" s="5" t="n"/>
+      <c r="E1" s="3" t="inlineStr"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="4" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -557,59 +541,75 @@
       </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>штук</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="7" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="3" t="n"/>
+      <c r="N2" s="4" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="2" t="n"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>диаметр</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="7" t="n"/>
+      <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
-      <c r="J3" s="7" t="n"/>
+      <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
-      <c r="N3" s="3" t="n"/>
+      <c r="N3" s="4" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="7" t="n"/>
-      <c r="B4" s="2" t="n"/>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>диаметр</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="7" t="n"/>
+      <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
-      <c r="J4" s="7" t="n"/>
+      <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="4" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="2" t="n"/>
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>НАПИЛЕНО ДОСКИ</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
@@ -619,109 +619,213 @@
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="4" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>0-4 с.</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>5 с.</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" s="7" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>6 с.</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="n"/>
-      <c r="H6" s="7" t="n"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>7 с.</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="7" t="n"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>некондиция</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="8" t="n"/>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>общая</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="8" t="n"/>
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>выхода</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="8" t="n"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="9" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="8" t="n"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>3 м</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="9" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="8" t="n"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2 м</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="9" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="8" t="n"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Итого:</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="9" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="2" t="n"/>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>НАПИЛЕНО ДОСКИ</t>
+        </is>
+      </c>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
+      <c r="D12" s="7" t="inlineStr"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
@@ -731,109 +835,213 @@
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
-      <c r="N12" s="3" t="n"/>
+      <c r="N12" s="4" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>0-4 с.</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>5 с.</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="n"/>
-      <c r="F13" s="7" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>6 с.</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>7 с.</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="n"/>
-      <c r="J13" s="7" t="n"/>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>некондиция</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="8" t="n"/>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t>общая</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="8" t="n"/>
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>выхода</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="8" t="n"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="9" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="8" t="n"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>3 м</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="9" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="8" t="n"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2 м</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="9" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
-      <c r="N18" s="8" t="n"/>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Итого:</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="9" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>НАПИЛЕНО ДОСКИ</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
+      <c r="D19" s="7" t="inlineStr"/>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
@@ -843,108 +1051,233 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
-      <c r="N19" s="3" t="n"/>
+      <c r="N19" s="4" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>0-4 с.</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>5 с.</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>6 с.</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="n"/>
-      <c r="H20" s="7" t="n"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>7 с.</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="n"/>
-      <c r="J20" s="7" t="n"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>некондиция</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="8" t="n"/>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>общая</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="8" t="n"/>
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>выхода</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="8" t="n"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="9" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="8" t="n"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>3 м</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="9" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="8" t="n"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2 м</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="9" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="10" t="n"/>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Итого:</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="11" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
+      <c r="N25" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="27">
+    <mergeCell ref="D20:E20"/>
     <mergeCell ref="D2:I2"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="J4:N4"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="E1:N1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
